--- a/SeleniumTests/TestDataFolder/TransactionTestDataValid.xlsx
+++ b/SeleniumTests/TestDataFolder/TransactionTestDataValid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B589288F-CB69-427D-9E5E-2BF6919C234D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A192C1-AF53-48FA-93CC-D071D130EAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39345" yWindow="2895" windowWidth="17280" windowHeight="9960" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SearchTransactionTestData" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="48">
   <si>
     <t>Search Text</t>
   </si>
@@ -57,12 +57,6 @@
     <t>Pending</t>
   </si>
   <si>
-    <t>YINV-102-251103115658</t>
-  </si>
-  <si>
-    <t>Testing Name</t>
-  </si>
-  <si>
     <t>Tab</t>
   </si>
   <si>
@@ -181,6 +175,15 @@
   </si>
   <si>
     <t>Oct</t>
+  </si>
+  <si>
+    <t>General Public</t>
+  </si>
+  <si>
+    <t>S001/T02/212</t>
+  </si>
+  <si>
+    <t>Dec</t>
   </si>
 </sst>
 </file>
@@ -216,10 +219,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +510,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -516,7 +518,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -524,15 +526,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
@@ -540,15 +542,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
@@ -556,7 +558,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>4</v>
@@ -574,12 +576,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -594,37 +596,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -639,12 +641,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -656,60 +658,75 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E39F3C-2E0C-4876-9773-194411ADF76A}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="80.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="54.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="87.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" t="s">
-        <v>29</v>
-      </c>
       <c r="J1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E2">
         <v>2025</v>
@@ -718,7 +735,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H2">
         <v>2026</v>
@@ -727,119 +744,119 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
         <v>34</v>
       </c>
-      <c r="J4" t="s">
-        <v>36</v>
-      </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E7">
         <v>2025</v>
@@ -848,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H7">
         <v>2026</v>
@@ -860,50 +877,50 @@
         <v>4</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
       </c>
       <c r="J8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" t="s">
         <v>36</v>
       </c>
-      <c r="K8" t="s">
-        <v>38</v>
-      </c>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9">
         <v>2025</v>
@@ -912,7 +929,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H9">
         <v>2026</v>
@@ -921,16 +938,16 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" t="s">
         <v>36</v>
       </c>
-      <c r="K9" t="s">
-        <v>38</v>
-      </c>
       <c r="L9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
